--- a/Projeto_com_fusaoSE_formula_1.xlsx
+++ b/Projeto_com_fusaoSE_formula_1.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rjuni\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rjuni\OneDrive\Área de Trabalho\JUNIOR\ESTUDO DE ANALISE DE DADOS\pasta de prjetos com excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{615DDA81-88FB-493A-BD35-B2E6E54ED41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDBE3A04-53C6-430D-8EDA-006DF69474C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="957" xr2:uid="{85B08948-7BCF-4007-BABB-111144F4B1B5}"/>
+    <workbookView xWindow="34215" yWindow="900" windowWidth="18975" windowHeight="11295" tabRatio="957" activeTab="1" xr2:uid="{85B08948-7BCF-4007-BABB-111144F4B1B5}"/>
   </bookViews>
   <sheets>
-    <sheet name="Exercicio1" sheetId="3" r:id="rId1"/>
-    <sheet name="Exercicio2" sheetId="8" r:id="rId2"/>
+    <sheet name="Treino" sheetId="3" r:id="rId1"/>
+    <sheet name="Treino 2" sheetId="8" r:id="rId2"/>
     <sheet name="ÍNDICE CORRESP" sheetId="6" state="hidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -2469,7 +2469,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2546,10 +2546,22 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="7" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2589,7 +2601,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top style="thin">
@@ -2615,6 +2627,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="4" tint="0.79998168889431442"/>
@@ -2622,7 +2635,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top style="thin">
@@ -2739,8 +2752,12 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{D801CA54-D910-4E4A-BDC6-FA3B03D4D0B9}" name="Vendedor" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{A4CB21AD-F60D-4EA3-8242-0EB9FD4F29A3}" name="Faturado" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{BBAE7579-7F82-4A56-B2BB-76B78C389B28}" name="Bônus" dataDxfId="1" dataCellStyle="Porcentagem"/>
-    <tableColumn id="4" xr3:uid="{4B10A2AF-FE30-4EDA-9D5D-54934374247A}" name="Salário" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{BBAE7579-7F82-4A56-B2BB-76B78C389B28}" name="Bônus" dataDxfId="1" dataCellStyle="Porcentagem">
+      <calculatedColumnFormula>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{4B10A2AF-FE30-4EDA-9D5D-54934374247A}" name="Salário" dataDxfId="0">
+      <calculatedColumnFormula>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9107,8 +9124,9 @@
   <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14.28515625" style="18" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" style="18" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="31" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="35" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
     <col min="7" max="9" width="12.28515625" customWidth="1"/>
   </cols>
@@ -9117,20 +9135,20 @@
       <c r="A1" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="30" t="s">
         <v>758</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="32" t="s">
         <v>757</v>
       </c>
       <c r="D1" s="29" t="s">
         <v>759</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="36" t="s">
         <v>760</v>
       </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
@@ -9139,8 +9157,14 @@
       <c r="B2" s="25">
         <v>58729</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="25"/>
+      <c r="C2" s="33">
+        <f>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</f>
+        <v>0.05</v>
+      </c>
+      <c r="D2" s="25">
+        <f>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</f>
+        <v>2936.4500000000003</v>
+      </c>
       <c r="G2" s="20" t="s">
         <v>328</v>
       </c>
@@ -9158,8 +9182,14 @@
       <c r="B3" s="26">
         <v>162517</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="26"/>
+      <c r="C3" s="34">
+        <f>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</f>
+        <v>0.1</v>
+      </c>
+      <c r="D3" s="26">
+        <f>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</f>
+        <v>16251.7</v>
+      </c>
       <c r="G3" s="21">
         <v>0</v>
       </c>
@@ -9177,8 +9207,14 @@
       <c r="B4" s="25">
         <v>432944</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="25"/>
+      <c r="C4" s="33">
+        <f>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="D4" s="25">
+        <f>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</f>
+        <v>129883.2</v>
+      </c>
       <c r="G4" s="21">
         <v>50001</v>
       </c>
@@ -9196,8 +9232,14 @@
       <c r="B5" s="26">
         <v>514342</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="26"/>
+      <c r="C5" s="34">
+        <f>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="D5" s="26">
+        <f>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</f>
+        <v>154302.6</v>
+      </c>
       <c r="G5" s="21">
         <v>100001</v>
       </c>
@@ -9215,8 +9257,14 @@
       <c r="B6" s="25">
         <v>214635</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="25"/>
+      <c r="C6" s="33">
+        <f>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</f>
+        <v>0.15</v>
+      </c>
+      <c r="D6" s="25">
+        <f>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</f>
+        <v>32195.25</v>
+      </c>
       <c r="G6" s="21">
         <v>200001</v>
       </c>
@@ -9234,8 +9282,14 @@
       <c r="B7" s="26">
         <v>239239</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="26"/>
+      <c r="C7" s="34">
+        <f>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</f>
+        <v>0.15</v>
+      </c>
+      <c r="D7" s="26">
+        <f>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</f>
+        <v>35885.85</v>
+      </c>
       <c r="G7" s="21">
         <v>300001</v>
       </c>
@@ -9253,8 +9307,14 @@
       <c r="B8" s="25">
         <v>40622</v>
       </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="25"/>
+      <c r="C8" s="33">
+        <f>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</f>
+        <v>0.02</v>
+      </c>
+      <c r="D8" s="25">
+        <f>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</f>
+        <v>812.44</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
@@ -9263,8 +9323,14 @@
       <c r="B9" s="26">
         <v>389479</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="26"/>
+      <c r="C9" s="34">
+        <f>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="D9" s="26">
+        <f>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</f>
+        <v>116843.7</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="27" t="s">
@@ -9273,8 +9339,14 @@
       <c r="B10" s="25">
         <v>553835</v>
       </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="25"/>
+      <c r="C10" s="33">
+        <f>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="D10" s="25">
+        <f>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</f>
+        <v>166150.5</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
@@ -9283,8 +9355,14 @@
       <c r="B11" s="26">
         <v>446282</v>
       </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="26"/>
+      <c r="C11" s="34">
+        <f>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="D11" s="26">
+        <f>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</f>
+        <v>133884.6</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
@@ -9293,8 +9371,14 @@
       <c r="B12" s="25">
         <v>310454</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="25"/>
+      <c r="C12" s="33">
+        <f>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="D12" s="25">
+        <f>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</f>
+        <v>93136.2</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
@@ -9303,8 +9387,14 @@
       <c r="B13" s="26">
         <v>523471</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="26"/>
+      <c r="C13" s="34">
+        <f>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="D13" s="26">
+        <f>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</f>
+        <v>157041.29999999999</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="27" t="s">
@@ -9313,8 +9403,14 @@
       <c r="B14" s="25">
         <v>54717</v>
       </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="25"/>
+      <c r="C14" s="33">
+        <f>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</f>
+        <v>0.05</v>
+      </c>
+      <c r="D14" s="25">
+        <f>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</f>
+        <v>2735.8500000000004</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
@@ -9323,8 +9419,14 @@
       <c r="B15" s="26">
         <v>398008</v>
       </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="26"/>
+      <c r="C15" s="34">
+        <f>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="D15" s="26">
+        <f>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</f>
+        <v>119402.4</v>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="27" t="s">
@@ -9333,8 +9435,14 @@
       <c r="B16" s="25">
         <v>70346</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="25"/>
+      <c r="C16" s="33">
+        <f>IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$3,$I$3,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$4,$I$4,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$5,$I$5,IF(Tabela2[[#This Row],[Faturado]]&lt;=$H$6,$I$6,$I$7))))</f>
+        <v>0.05</v>
+      </c>
+      <c r="D16" s="25">
+        <f>Tabela2[[#This Row],[Faturado]]*Tabela2[[#This Row],[Bônus]]</f>
+        <v>3517.3</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
